--- a/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3001  PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3001  PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F957C703-DADB-4AE7-AD52-C960245E6F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB04D4D1-A7BE-42BA-923E-582823EF8FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>Falta</t>
   </si>
@@ -129,13 +129,79 @@
   </si>
   <si>
     <t>201651237786 - WENDEL SANTANA DE FREITAS</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>não fez</t>
+  </si>
+  <si>
+    <t>https://github.com/ArthurPedrada/Se_Ligue_ae</t>
+  </si>
+  <si>
+    <t>https://github.com/aryaneandrade/projeto-monitorias-uniruy</t>
+  </si>
+  <si>
+    <t>https://github.com/GabriellaMizrach/Sistema_de_Controle_de_Estoque_CRUD</t>
+  </si>
+  <si>
+    <t>https://github.com/GeisaMiranda/sistema-salao-agendamento</t>
+  </si>
+  <si>
+    <t>https://github.com/Hanna280/clinica.odontologica</t>
+  </si>
+  <si>
+    <t>https://github.com/LuffyBaiano27/L.I.A---Laboratorio-de-inteligencia-artistica</t>
+  </si>
+  <si>
+    <t>https://github.com/helleenlara/FinancasPessoais</t>
+  </si>
+  <si>
+    <t>https://github.com/lariandrill/Projeto-de-mensagens-WEB</t>
+  </si>
+  <si>
+    <t>https://github.com/Marcosadb/trabalho_python_rad_bet</t>
+  </si>
+  <si>
+    <t>https://github.com/codewithmaria/Projeto-Python-RAD</t>
+  </si>
+  <si>
+    <t>https://github.com/mariaeduardadias5/trabalhoradpython</t>
+  </si>
+  <si>
+    <t>https://github.com/melissagsb/cantina-universitaria</t>
+  </si>
+  <si>
+    <t>https://github.com/machadorenata119-del/Projeto-de-Python-Rad</t>
+  </si>
+  <si>
+    <t>https://github.com/Thallycs/Nexus360</t>
+  </si>
+  <si>
+    <t>Iberostar; https://thunderous-jelly-483397.netlify.app/</t>
+  </si>
+  <si>
+    <t>não app render</t>
+  </si>
+  <si>
+    <t>https://github.com/tiagogc15/Projeto-Biblioteca</t>
+  </si>
+  <si>
+    <t>não postou no SAVA; https://github.com/tiagogc15/Cadastro-Produtos-Tkinter</t>
+  </si>
+  <si>
+    <t>não postou link GitHub no SAVA</t>
+  </si>
+  <si>
+    <t>não apresentou; não cloud</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,8 +228,23 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,8 +257,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -359,11 +446,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -374,41 +512,62 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -741,594 +900,771 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="84.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8">
-        <v>0</v>
+      <c r="B2" s="17">
+        <v>5</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
       </c>
       <c r="D2" s="8">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8">
         <v>0.5</v>
       </c>
-      <c r="E2" s="8">
+      <c r="F2" s="8">
         <v>0.9</v>
       </c>
-      <c r="F2" s="9">
-        <f>$B$2/7*4</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="9">
+        <f>$C$2/7*4</f>
+        <v>0</v>
+      </c>
       <c r="H2" s="10">
-        <f>F2+G2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+        <v>5.5</v>
+      </c>
+      <c r="I2" s="10">
+        <f>G2+H2</f>
+        <v>5.5</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
+      <c r="B3" s="18">
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
       </c>
       <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.9</v>
       </c>
-      <c r="E3" s="4">
+      <c r="F3" s="4">
         <v>0.3</v>
       </c>
-      <c r="F3" s="5">
-        <f t="shared" ref="F3:F21" si="0">$B$2/7*4</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G21" si="0">$C$2/7*4</f>
+        <v>0</v>
+      </c>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:H21" si="1">F3+G3</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I21" si="1">G3+H3</f>
+        <v>6</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
+      <c r="B4" s="18">
+        <v>16</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.8</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <v>0.9</v>
       </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H4" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
+      <c r="B5" s="18">
+        <v>7</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
         <v>0.8</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>0.7</v>
       </c>
-      <c r="F5" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H5" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="13"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
+      <c r="B6" s="18">
+        <v>9</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.7</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>0.8</v>
       </c>
-      <c r="F6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
+      <c r="B7" s="18">
+        <v>14</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
       </c>
       <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.6</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>0.1</v>
       </c>
-      <c r="F7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="13"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="4">
-        <v>0</v>
+      <c r="B8" s="18">
+        <v>17</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>0.5</v>
       </c>
-      <c r="F8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="13"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="4">
-        <v>0</v>
+      <c r="B9" s="18">
+        <v>17</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4">
         <v>0.6</v>
       </c>
-      <c r="F9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="6"/>
+      <c r="F9" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="13"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="4">
-        <v>0</v>
+      <c r="B10" s="18">
+        <v>1</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>0.4</v>
       </c>
-      <c r="F10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="4">
-        <v>0</v>
+      <c r="B11" s="18">
+        <v>3</v>
       </c>
       <c r="C11" s="4">
         <v>0</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
         <v>0.3</v>
       </c>
-      <c r="F11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="13"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
+      <c r="B12" s="18">
+        <v>4</v>
       </c>
       <c r="C12" s="4">
         <v>0</v>
       </c>
       <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <v>0.9</v>
       </c>
-      <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
+      <c r="B13" s="18">
+        <v>6</v>
       </c>
       <c r="C13" s="4">
         <v>0</v>
       </c>
       <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
         <v>0.6</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>0.4</v>
       </c>
-      <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4">
-        <v>0</v>
+      <c r="B14" s="18">
+        <v>2</v>
       </c>
       <c r="C14" s="4">
         <v>0</v>
       </c>
       <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
         <v>0.5</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>0.6</v>
       </c>
-      <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="4">
-        <v>0</v>
+      <c r="B15" s="18">
+        <v>12</v>
       </c>
       <c r="C15" s="4">
         <v>0</v>
       </c>
       <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
         <v>0.6</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>0.5</v>
       </c>
-      <c r="F15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="4">
-        <v>0</v>
+      <c r="B16" s="18">
+        <v>11</v>
       </c>
       <c r="C16" s="4">
         <v>0</v>
       </c>
       <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
         <v>0.3</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>0.7</v>
       </c>
-      <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
+      <c r="B17" s="24"/>
       <c r="C17" s="4">
         <v>0</v>
       </c>
       <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
         <v>0.4</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="6"/>
+      <c r="F17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="4">
-        <v>0</v>
+      <c r="B18" s="18">
+        <v>13</v>
       </c>
       <c r="C18" s="4">
         <v>0</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
         <v>0.5</v>
       </c>
-      <c r="F18" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="13"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
+      <c r="B19" s="18">
+        <v>5</v>
       </c>
       <c r="C19" s="4">
         <v>0</v>
       </c>
       <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
         <v>0.5</v>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" s="4">
         <v>0.7</v>
       </c>
-      <c r="F19" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="13"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+        <v>5.5</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="4">
-        <v>0</v>
+      <c r="B20" s="18">
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>0</v>
       </c>
       <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
         <v>0.6</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <v>0.9</v>
       </c>
-      <c r="F20" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="13"/>
-    </row>
-    <row r="21" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+        <v>5.5</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="15">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="18"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{C329E086-8FD1-40B6-9E0D-55D81D663B7A}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{F02F9A40-F01F-4A01-BA7F-CA9C84022221}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{6E9E5E46-0B39-460F-BCFB-EF5F3D081E33}"/>
+    <hyperlink ref="J6" r:id="rId4" xr:uid="{3CE889BD-FC01-40EF-B10B-BC6910023BEC}"/>
+    <hyperlink ref="J7" r:id="rId5" xr:uid="{046FBD93-9F95-4238-9F31-DDE5E581363F}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{B76EA550-7914-43C3-A3AD-C19B9F1CDB73}"/>
+    <hyperlink ref="J9" r:id="rId7" xr:uid="{4D52BDA9-B484-4FB0-A2C8-05DB59441337}"/>
+    <hyperlink ref="J10" r:id="rId8" xr:uid="{F0FDC899-F077-4096-8883-3A6D4B1C8916}"/>
+    <hyperlink ref="J11" r:id="rId9" xr:uid="{9D3768AF-6769-46E2-A188-3F95BAB5A875}"/>
+    <hyperlink ref="J12" r:id="rId10" xr:uid="{44F91CDF-C04F-4124-B1AC-847678478229}"/>
+    <hyperlink ref="J14" r:id="rId11" xr:uid="{0C9040F6-08E6-4784-9CCB-D144C86FB900}"/>
+    <hyperlink ref="J15" r:id="rId12" xr:uid="{8EE556C9-6BC5-465D-8889-3935319CBB6B}"/>
+    <hyperlink ref="J16" r:id="rId13" xr:uid="{0403F244-7998-47D5-B6B4-246045C174BE}"/>
+    <hyperlink ref="J18" r:id="rId14" xr:uid="{F5FDE7A0-4892-4F45-B1EC-ECD6517DFF43}"/>
+    <hyperlink ref="J19" r:id="rId15" xr:uid="{9BD2AE43-DC58-4541-BF8A-4FD2E8BDADA4}"/>
+    <hyperlink ref="J20" r:id="rId16" xr:uid="{2C7BE1E8-EAAE-4091-9DCD-3FF9714E868F}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3001  PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3001  PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB04D4D1-A7BE-42BA-923E-582823EF8FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C6D9CC-3101-4B2D-86A0-AECF1ECDD738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>Falta</t>
   </si>
@@ -161,15 +161,9 @@
     <t>https://github.com/lariandrill/Projeto-de-mensagens-WEB</t>
   </si>
   <si>
-    <t>https://github.com/Marcosadb/trabalho_python_rad_bet</t>
-  </si>
-  <si>
     <t>https://github.com/codewithmaria/Projeto-Python-RAD</t>
   </si>
   <si>
-    <t>https://github.com/mariaeduardadias5/trabalhoradpython</t>
-  </si>
-  <si>
     <t>https://github.com/melissagsb/cantina-universitaria</t>
   </si>
   <si>
@@ -182,26 +176,112 @@
     <t>Iberostar; https://thunderous-jelly-483397.netlify.app/</t>
   </si>
   <si>
-    <t>não app render</t>
-  </si>
-  <si>
     <t>https://github.com/tiagogc15/Projeto-Biblioteca</t>
   </si>
   <si>
-    <t>não postou no SAVA; https://github.com/tiagogc15/Cadastro-Produtos-Tkinter</t>
-  </si>
-  <si>
-    <t>não postou link GitHub no SAVA</t>
-  </si>
-  <si>
-    <t>não apresentou; não cloud</t>
+    <t xml:space="preserve">https://github.com/deivomaciel/Maat-System </t>
+  </si>
+  <si>
+    <t>https://se-ligue-ae.onrender.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domínio próprio - hospedado AWS
+https://www.monitorias.andops.com.br </t>
+  </si>
+  <si>
+    <t>https://maat-system.vercel.app/</t>
+  </si>
+  <si>
+    <t>https://sistemadecontroledeestoquecrud-8difgl7qc2tozjksrm6nny.streamlit.app/</t>
+  </si>
+  <si>
+    <t>https://sistema-salao-agendamento-1.onrender.com/</t>
+  </si>
+  <si>
+    <t>https://luffybaiano27.pythonanywhere.com/</t>
+  </si>
+  <si>
+    <t>https://financaspessoais-mt7o.onrender.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Disponibilizar no README o link app</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://projeto-de-mensagens-web.onrender.com/</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/Marcosadb/trabalho_python_rad_bet </t>
+  </si>
+  <si>
+    <t>https://projeto-python-rad-ktnzlvqcljhockrzfzp73u.streamlit.app/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mariaeduardadias5/trabalhoradpython </t>
+  </si>
+  <si>
+    <t>https://mariaeduardadias5.pythonanywhere.com</t>
+  </si>
+  <si>
+    <t>https://melissagsb.pythonanywhere.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LOCALHOST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; Não cloud app; bd  sqlite3; sem README</t>
+    </r>
+  </si>
+  <si>
+    <t>postou no SAVA ATRAsado; https://github.com/tiagogc15/Cadastro-Produtos-Tkinter
+README pobre; BD SQLITE3
+https://projeto-biblioteca-production.up.railway.app/login/</t>
+  </si>
+  <si>
+    <t>SEM README; BD SQLITE3; Disponibilizar link no READMED / PPT; https://nexus360-qyx7.onrender.com/</t>
+  </si>
+  <si>
+    <t>LOCALHOST; não apresentou; não cloud; SQLITE;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +323,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -501,7 +589,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -532,7 +620,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -556,7 +643,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -565,6 +651,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -912,13 +1007,14 @@
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="77" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -950,7 +1046,7 @@
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>5</v>
       </c>
       <c r="C2" s="8">
@@ -970,24 +1066,24 @@
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I2" s="10">
         <f>G2+H2</f>
-        <v>5.5</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>46</v>
+        <v>5</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>10</v>
       </c>
       <c r="C3" s="4">
@@ -1013,15 +1109,18 @@
         <f t="shared" ref="I3:I21" si="1">G3+H3</f>
         <v>6</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="23" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K3" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>16</v>
       </c>
       <c r="C4" s="4">
@@ -1047,15 +1146,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="23" t="s">
         <v>34</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>7</v>
       </c>
       <c r="C5" s="4">
@@ -1075,21 +1177,24 @@
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>9</v>
       </c>
       <c r="C6" s="4">
@@ -1115,15 +1220,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="23" t="s">
         <v>35</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>14</v>
       </c>
       <c r="C7" s="4">
@@ -1149,15 +1257,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="23" t="s">
         <v>36</v>
       </c>
+      <c r="K7" s="25" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>17</v>
       </c>
       <c r="C8" s="4">
@@ -1183,18 +1294,18 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K8" t="s">
-        <v>52</v>
+      <c r="K8" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>17</v>
       </c>
       <c r="C9" s="4">
@@ -1220,18 +1331,18 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K9" t="s">
-        <v>52</v>
+      <c r="K9" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>1</v>
       </c>
       <c r="C10" s="4">
@@ -1257,15 +1368,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="23" t="s">
         <v>38</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>3</v>
       </c>
       <c r="C11" s="4">
@@ -1291,15 +1405,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="23" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K11" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>4</v>
       </c>
       <c r="C12" s="4">
@@ -1325,15 +1442,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="23" t="s">
         <v>40</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <v>6</v>
       </c>
       <c r="C13" s="4">
@@ -1353,21 +1473,24 @@
         <v>0</v>
       </c>
       <c r="H13" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>41</v>
+        <v>4</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>2</v>
       </c>
       <c r="C14" s="4">
@@ -1393,15 +1516,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>42</v>
+      <c r="J14" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>12</v>
       </c>
       <c r="C15" s="4">
@@ -1427,15 +1553,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>43</v>
+      <c r="J15" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>11</v>
       </c>
       <c r="C16" s="4">
@@ -1461,15 +1590,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>44</v>
+      <c r="J16" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4">
         <v>0</v>
       </c>
@@ -1493,15 +1625,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="19" t="s">
         <v>32</v>
       </c>
+      <c r="K17" s="27"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>13</v>
       </c>
       <c r="C18" s="4">
@@ -1527,18 +1660,18 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" t="s">
         <v>45</v>
-      </c>
-      <c r="K18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>5</v>
       </c>
       <c r="C19" s="4">
@@ -1558,24 +1691,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="6">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>46</v>
+        <v>5</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>15</v>
       </c>
       <c r="C20" s="4">
@@ -1595,50 +1728,51 @@
         <v>0</v>
       </c>
       <c r="H20" s="6">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" t="s">
-        <v>50</v>
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14">
+      <c r="B21" s="21"/>
+      <c r="C21" s="12">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="15">
-        <v>0</v>
-      </c>
-      <c r="I21" s="15">
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="29" t="s">
         <v>32</v>
       </c>
+      <c r="K21" s="27"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1663,8 +1797,20 @@
     <hyperlink ref="J18" r:id="rId14" xr:uid="{F5FDE7A0-4892-4F45-B1EC-ECD6517DFF43}"/>
     <hyperlink ref="J19" r:id="rId15" xr:uid="{9BD2AE43-DC58-4541-BF8A-4FD2E8BDADA4}"/>
     <hyperlink ref="J20" r:id="rId16" xr:uid="{2C7BE1E8-EAAE-4091-9DCD-3FF9714E868F}"/>
+    <hyperlink ref="J5" r:id="rId17" xr:uid="{8539A614-7799-49E5-9B78-8A97D88B43AD}"/>
+    <hyperlink ref="K3" r:id="rId18" xr:uid="{F097916C-4A62-4EAD-9EFD-748773CA7C52}"/>
+    <hyperlink ref="K5" r:id="rId19" xr:uid="{8604EE40-8DD4-48D0-BC58-6E2F3E0A758B}"/>
+    <hyperlink ref="K6" r:id="rId20" xr:uid="{4802825E-F830-45E8-A88B-66FC7F69280F}"/>
+    <hyperlink ref="K7" r:id="rId21" xr:uid="{EF85404C-45AD-4145-840D-F7732E388CB9}"/>
+    <hyperlink ref="K10" r:id="rId22" xr:uid="{A28B05B3-46A6-4B10-9423-4614A79AFC1C}"/>
+    <hyperlink ref="K11" r:id="rId23" xr:uid="{1664BBC8-1022-43C2-B249-7D724436D55D}"/>
+    <hyperlink ref="K12" r:id="rId24" display="https://projeto-de-mensagens-web.onrender.com/" xr:uid="{D66E3EBA-724C-4F93-965F-46E07E7C7F10}"/>
+    <hyperlink ref="J13" r:id="rId25" xr:uid="{1F606B7E-3483-439C-8AD0-79A3EF463063}"/>
+    <hyperlink ref="K14" r:id="rId26" xr:uid="{39879EC2-5994-4AB4-9FCE-CAB80A2AA957}"/>
+    <hyperlink ref="K15" r:id="rId27" xr:uid="{CFFD3181-BBE0-41DD-A476-5181DD9D4B60}"/>
+    <hyperlink ref="K16" r:id="rId28" xr:uid="{DE0D148A-01CB-4601-8571-5AE2DDAB6C95}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
 </worksheet>
 </file>